--- a/АБК/Том СОТС АБК/Журнал входного контроля СОТС АБК.xlsx
+++ b/АБК/Том СОТС АБК/Журнал входного контроля СОТС АБК.xlsx
@@ -576,7 +576,7 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Рабочая документация 16/1/26-СОТС-Р, лист 5; исполнительная документация 16/1/26-ИД-АБК, лист 7. Количество материалов — по АОСР № 1-СОТС-АБК, 2-СОТС-АБК, 3-СОТС-АБК; оборудование — по исполнительной документации.</t>
+          <t>Рабочая документация 16/1/26-СОТС-Р, лист 5; исполнительная документация 16/1/26-СОТС-ИД-АБК, лист 2. Спецификация 16/1/26-СОТС-ИД-АБК.СО. Количество материалов — по АОСР № 1-СОТС-АБК, 2-СОТС-АБК, 3-СОТС-АБК; оборудование — по исполнительной документации.</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 7</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 7</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 7</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Оповещатель охранно-пожарный звуковой адресный, С2000-ОСТ исп.01 (по УГО ИД) (поз. BIALS)</t>
+          <t>Оповещатель охранно-пожарный звуковой адресный, С2000-ОПЗ (поз. BIALS)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 7</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 7</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 7</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Контроллер двухпроводной линии, С2000-КДЛ (поз. ARK1)</t>
+          <t>Контроллер двухпроводной линии, два интерфейса RS-485, С2000-КДЛ-2И исп.01 (поз. ARK1)</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 7</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 7</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 7</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>

--- a/АБК/Том СОТС АБК/Журнал входного контроля СОТС АБК.xlsx
+++ b/АБК/Том СОТС АБК/Журнал входного контроля СОТС АБК.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1568,49 +1568,102 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Батарея аккумуляторная 12 В 18 А·ч (в шкафу ШПС-24, UG3), DT 12В 18Ач</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Паспорт (руководство по эксплуатации) изготовителя</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Внешний осмотр, маркировка, комплектность — без замечаний. Паспорт изготовителя в наличии (оригинал).</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>Соответствует. Допущено к применению</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Иванчук М.В.</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>ИД лист 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Ответственный за входной контроль (лицо, выполняющее работы)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>начальник отдела систем технической безопасности ООО «АльтЭн» Иванчук М.В.</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="I36" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Представитель лица, осуществляющего строительство</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>руководитель проекта Белоногов И.Ю.</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I38" s="14" t="inlineStr">
+      <c r="I39" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
@@ -1618,24 +1671,24 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A34:K34"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A11:K11"/>
+    <mergeCell ref="G36:H36"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G39:H39"/>
     <mergeCell ref="A6:K6"/>
-    <mergeCell ref="G38:H38"/>
     <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="A8:K8"/>
-    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="A38:K38"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A9:K9"/>
   </mergeCells>
